--- a/automation/reports/Excel/Failed_Test_Cases.xlsx
+++ b/automation/reports/Excel/Failed_Test_Cases.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-12 09:55:15</t>
+          <t>2026-08-12 11:08:43</t>
         </is>
       </c>
     </row>

--- a/automation/reports/Excel/Failed_Test_Cases.xlsx
+++ b/automation/reports/Excel/Failed_Test_Cases.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-12 11:08:43</t>
+          <t>2026-08-19 09:31:16</t>
         </is>
       </c>
     </row>
